--- a/russian_data/processed/DATASET.xlsx
+++ b/russian_data/processed/DATASET.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -20,13 +20,16 @@
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
   </numFmts>
-  <fonts count="1">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -37,7 +40,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -45,12 +48,21 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
@@ -421,39 +433,39 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>date</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>ret_t</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>rpo</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>rea_t</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>delta_world</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>delta_non_rus</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="1" t="n">
+      <c r="A2" s="2" t="n">
         <v>36526</v>
       </c>
       <c r="B2" t="n">
@@ -473,7 +485,7 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="1" t="n">
+      <c r="A3" s="2" t="n">
         <v>36557</v>
       </c>
       <c r="B3" t="n">
@@ -493,7 +505,7 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="1" t="n">
+      <c r="A4" s="2" t="n">
         <v>36586</v>
       </c>
       <c r="B4" t="n">
@@ -513,7 +525,7 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="1" t="n">
+      <c r="A5" s="2" t="n">
         <v>36617</v>
       </c>
       <c r="B5" t="n">
@@ -533,7 +545,7 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="1" t="n">
+      <c r="A6" s="2" t="n">
         <v>36647</v>
       </c>
       <c r="B6" t="n">
@@ -553,7 +565,7 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="1" t="n">
+      <c r="A7" s="2" t="n">
         <v>36678</v>
       </c>
       <c r="B7" t="n">
@@ -573,7 +585,7 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="1" t="n">
+      <c r="A8" s="2" t="n">
         <v>36708</v>
       </c>
       <c r="B8" t="n">
@@ -593,7 +605,7 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="1" t="n">
+      <c r="A9" s="2" t="n">
         <v>36739</v>
       </c>
       <c r="B9" t="n">
@@ -613,7 +625,7 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="1" t="n">
+      <c r="A10" s="2" t="n">
         <v>36770</v>
       </c>
       <c r="B10" t="n">
@@ -633,7 +645,7 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="1" t="n">
+      <c r="A11" s="2" t="n">
         <v>36800</v>
       </c>
       <c r="B11" t="n">
@@ -653,7 +665,7 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="1" t="n">
+      <c r="A12" s="2" t="n">
         <v>36831</v>
       </c>
       <c r="B12" t="n">
@@ -673,7 +685,7 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="1" t="n">
+      <c r="A13" s="2" t="n">
         <v>36861</v>
       </c>
       <c r="B13" t="n">
@@ -693,7 +705,7 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="1" t="n">
+      <c r="A14" s="2" t="n">
         <v>36892</v>
       </c>
       <c r="B14" t="n">
@@ -713,7 +725,7 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="1" t="n">
+      <c r="A15" s="2" t="n">
         <v>36923</v>
       </c>
       <c r="B15" t="n">
@@ -733,7 +745,7 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="1" t="n">
+      <c r="A16" s="2" t="n">
         <v>36951</v>
       </c>
       <c r="B16" t="n">
@@ -753,7 +765,7 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="1" t="n">
+      <c r="A17" s="2" t="n">
         <v>36982</v>
       </c>
       <c r="B17" t="n">
@@ -773,7 +785,7 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="1" t="n">
+      <c r="A18" s="2" t="n">
         <v>37012</v>
       </c>
       <c r="B18" t="n">
@@ -793,7 +805,7 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="1" t="n">
+      <c r="A19" s="2" t="n">
         <v>37043</v>
       </c>
       <c r="B19" t="n">
@@ -813,7 +825,7 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="1" t="n">
+      <c r="A20" s="2" t="n">
         <v>37073</v>
       </c>
       <c r="B20" t="n">
@@ -833,7 +845,7 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="1" t="n">
+      <c r="A21" s="2" t="n">
         <v>37104</v>
       </c>
       <c r="B21" t="n">
@@ -853,7 +865,7 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="1" t="n">
+      <c r="A22" s="2" t="n">
         <v>37135</v>
       </c>
       <c r="B22" t="n">
@@ -873,7 +885,7 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="1" t="n">
+      <c r="A23" s="2" t="n">
         <v>37165</v>
       </c>
       <c r="B23" t="n">
@@ -893,7 +905,7 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="1" t="n">
+      <c r="A24" s="2" t="n">
         <v>37196</v>
       </c>
       <c r="B24" t="n">
@@ -913,7 +925,7 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="1" t="n">
+      <c r="A25" s="2" t="n">
         <v>37226</v>
       </c>
       <c r="B25" t="n">
@@ -933,7 +945,7 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="1" t="n">
+      <c r="A26" s="2" t="n">
         <v>37257</v>
       </c>
       <c r="B26" t="n">
@@ -953,7 +965,7 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="1" t="n">
+      <c r="A27" s="2" t="n">
         <v>37288</v>
       </c>
       <c r="B27" t="n">
@@ -973,11 +985,11 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="1" t="n">
+      <c r="A28" s="2" t="n">
         <v>37316</v>
       </c>
       <c r="B28" t="n">
-        <v>13.13691608355108</v>
+        <v>13.13691608355109</v>
       </c>
       <c r="C28" t="n">
         <v>2.524719732166175</v>
@@ -993,7 +1005,7 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="1" t="n">
+      <c r="A29" s="2" t="n">
         <v>37347</v>
       </c>
       <c r="B29" t="n">
@@ -1013,7 +1025,7 @@
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="1" t="n">
+      <c r="A30" s="2" t="n">
         <v>37377</v>
       </c>
       <c r="B30" t="n">
@@ -1033,7 +1045,7 @@
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="1" t="n">
+      <c r="A31" s="2" t="n">
         <v>37408</v>
       </c>
       <c r="B31" t="n">
@@ -1053,7 +1065,7 @@
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="1" t="n">
+      <c r="A32" s="2" t="n">
         <v>37438</v>
       </c>
       <c r="B32" t="n">
@@ -1073,7 +1085,7 @@
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="1" t="n">
+      <c r="A33" s="2" t="n">
         <v>37469</v>
       </c>
       <c r="B33" t="n">
@@ -1093,7 +1105,7 @@
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="1" t="n">
+      <c r="A34" s="2" t="n">
         <v>37500</v>
       </c>
       <c r="B34" t="n">
@@ -1113,7 +1125,7 @@
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="1" t="n">
+      <c r="A35" s="2" t="n">
         <v>37530</v>
       </c>
       <c r="B35" t="n">
@@ -1133,7 +1145,7 @@
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="1" t="n">
+      <c r="A36" s="2" t="n">
         <v>37561</v>
       </c>
       <c r="B36" t="n">
@@ -1153,7 +1165,7 @@
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="1" t="n">
+      <c r="A37" s="2" t="n">
         <v>37591</v>
       </c>
       <c r="B37" t="n">
@@ -1173,7 +1185,7 @@
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="1" t="n">
+      <c r="A38" s="2" t="n">
         <v>37622</v>
       </c>
       <c r="B38" t="n">
@@ -1193,7 +1205,7 @@
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="1" t="n">
+      <c r="A39" s="2" t="n">
         <v>37653</v>
       </c>
       <c r="B39" t="n">
@@ -1213,7 +1225,7 @@
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="1" t="n">
+      <c r="A40" s="2" t="n">
         <v>37681</v>
       </c>
       <c r="B40" t="n">
@@ -1233,7 +1245,7 @@
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="1" t="n">
+      <c r="A41" s="2" t="n">
         <v>37712</v>
       </c>
       <c r="B41" t="n">
@@ -1253,7 +1265,7 @@
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="1" t="n">
+      <c r="A42" s="2" t="n">
         <v>37742</v>
       </c>
       <c r="B42" t="n">
@@ -1273,7 +1285,7 @@
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="1" t="n">
+      <c r="A43" s="2" t="n">
         <v>37773</v>
       </c>
       <c r="B43" t="n">
@@ -1293,7 +1305,7 @@
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="1" t="n">
+      <c r="A44" s="2" t="n">
         <v>37803</v>
       </c>
       <c r="B44" t="n">
@@ -1313,7 +1325,7 @@
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="1" t="n">
+      <c r="A45" s="2" t="n">
         <v>37834</v>
       </c>
       <c r="B45" t="n">
@@ -1333,7 +1345,7 @@
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="1" t="n">
+      <c r="A46" s="2" t="n">
         <v>37865</v>
       </c>
       <c r="B46" t="n">
@@ -1353,7 +1365,7 @@
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="1" t="n">
+      <c r="A47" s="2" t="n">
         <v>37895</v>
       </c>
       <c r="B47" t="n">
@@ -1373,7 +1385,7 @@
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="1" t="n">
+      <c r="A48" s="2" t="n">
         <v>37926</v>
       </c>
       <c r="B48" t="n">
@@ -1393,7 +1405,7 @@
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="1" t="n">
+      <c r="A49" s="2" t="n">
         <v>37956</v>
       </c>
       <c r="B49" t="n">
@@ -1413,7 +1425,7 @@
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="1" t="n">
+      <c r="A50" s="2" t="n">
         <v>37987</v>
       </c>
       <c r="B50" t="n">
@@ -1433,7 +1445,7 @@
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="1" t="n">
+      <c r="A51" s="2" t="n">
         <v>38018</v>
       </c>
       <c r="B51" t="n">
@@ -1453,7 +1465,7 @@
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="1" t="n">
+      <c r="A52" s="2" t="n">
         <v>38047</v>
       </c>
       <c r="B52" t="n">
@@ -1473,7 +1485,7 @@
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="1" t="n">
+      <c r="A53" s="2" t="n">
         <v>38078</v>
       </c>
       <c r="B53" t="n">
@@ -1493,7 +1505,7 @@
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="1" t="n">
+      <c r="A54" s="2" t="n">
         <v>38108</v>
       </c>
       <c r="B54" t="n">
@@ -1513,7 +1525,7 @@
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="1" t="n">
+      <c r="A55" s="2" t="n">
         <v>38139</v>
       </c>
       <c r="B55" t="n">
@@ -1533,7 +1545,7 @@
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="1" t="n">
+      <c r="A56" s="2" t="n">
         <v>38169</v>
       </c>
       <c r="B56" t="n">
@@ -1553,7 +1565,7 @@
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="1" t="n">
+      <c r="A57" s="2" t="n">
         <v>38200</v>
       </c>
       <c r="B57" t="n">
@@ -1573,7 +1585,7 @@
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="1" t="n">
+      <c r="A58" s="2" t="n">
         <v>38231</v>
       </c>
       <c r="B58" t="n">
@@ -1593,7 +1605,7 @@
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="1" t="n">
+      <c r="A59" s="2" t="n">
         <v>38261</v>
       </c>
       <c r="B59" t="n">
@@ -1613,7 +1625,7 @@
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="1" t="n">
+      <c r="A60" s="2" t="n">
         <v>38292</v>
       </c>
       <c r="B60" t="n">
@@ -1633,7 +1645,7 @@
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="1" t="n">
+      <c r="A61" s="2" t="n">
         <v>38322</v>
       </c>
       <c r="B61" t="n">
@@ -1653,7 +1665,7 @@
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="1" t="n">
+      <c r="A62" s="2" t="n">
         <v>38353</v>
       </c>
       <c r="B62" t="n">
@@ -1673,7 +1685,7 @@
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="1" t="n">
+      <c r="A63" s="2" t="n">
         <v>38384</v>
       </c>
       <c r="B63" t="n">
@@ -1693,7 +1705,7 @@
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="1" t="n">
+      <c r="A64" s="2" t="n">
         <v>38412</v>
       </c>
       <c r="B64" t="n">
@@ -1713,7 +1725,7 @@
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="1" t="n">
+      <c r="A65" s="2" t="n">
         <v>38443</v>
       </c>
       <c r="B65" t="n">
@@ -1733,7 +1745,7 @@
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="1" t="n">
+      <c r="A66" s="2" t="n">
         <v>38473</v>
       </c>
       <c r="B66" t="n">
@@ -1753,7 +1765,7 @@
       </c>
     </row>
     <row r="67">
-      <c r="A67" s="1" t="n">
+      <c r="A67" s="2" t="n">
         <v>38504</v>
       </c>
       <c r="B67" t="n">
@@ -1773,7 +1785,7 @@
       </c>
     </row>
     <row r="68">
-      <c r="A68" s="1" t="n">
+      <c r="A68" s="2" t="n">
         <v>38534</v>
       </c>
       <c r="B68" t="n">
@@ -1793,7 +1805,7 @@
       </c>
     </row>
     <row r="69">
-      <c r="A69" s="1" t="n">
+      <c r="A69" s="2" t="n">
         <v>38565</v>
       </c>
       <c r="B69" t="n">
@@ -1813,7 +1825,7 @@
       </c>
     </row>
     <row r="70">
-      <c r="A70" s="1" t="n">
+      <c r="A70" s="2" t="n">
         <v>38596</v>
       </c>
       <c r="B70" t="n">
@@ -1833,7 +1845,7 @@
       </c>
     </row>
     <row r="71">
-      <c r="A71" s="1" t="n">
+      <c r="A71" s="2" t="n">
         <v>38626</v>
       </c>
       <c r="B71" t="n">
@@ -1853,7 +1865,7 @@
       </c>
     </row>
     <row r="72">
-      <c r="A72" s="1" t="n">
+      <c r="A72" s="2" t="n">
         <v>38657</v>
       </c>
       <c r="B72" t="n">
@@ -1873,7 +1885,7 @@
       </c>
     </row>
     <row r="73">
-      <c r="A73" s="1" t="n">
+      <c r="A73" s="2" t="n">
         <v>38687</v>
       </c>
       <c r="B73" t="n">
@@ -1893,7 +1905,7 @@
       </c>
     </row>
     <row r="74">
-      <c r="A74" s="1" t="n">
+      <c r="A74" s="2" t="n">
         <v>38718</v>
       </c>
       <c r="B74" t="n">
@@ -1913,7 +1925,7 @@
       </c>
     </row>
     <row r="75">
-      <c r="A75" s="1" t="n">
+      <c r="A75" s="2" t="n">
         <v>38749</v>
       </c>
       <c r="B75" t="n">
@@ -1933,7 +1945,7 @@
       </c>
     </row>
     <row r="76">
-      <c r="A76" s="1" t="n">
+      <c r="A76" s="2" t="n">
         <v>38777</v>
       </c>
       <c r="B76" t="n">
@@ -1953,11 +1965,11 @@
       </c>
     </row>
     <row r="77">
-      <c r="A77" s="1" t="n">
+      <c r="A77" s="2" t="n">
         <v>38808</v>
       </c>
       <c r="B77" t="n">
-        <v>12.67788644118132</v>
+        <v>12.67788644118133</v>
       </c>
       <c r="C77" t="n">
         <v>3.43708444913175</v>
@@ -1973,7 +1985,7 @@
       </c>
     </row>
     <row r="78">
-      <c r="A78" s="1" t="n">
+      <c r="A78" s="2" t="n">
         <v>38838</v>
       </c>
       <c r="B78" t="n">
@@ -1993,7 +2005,7 @@
       </c>
     </row>
     <row r="79">
-      <c r="A79" s="1" t="n">
+      <c r="A79" s="2" t="n">
         <v>38869</v>
       </c>
       <c r="B79" t="n">
@@ -2013,7 +2025,7 @@
       </c>
     </row>
     <row r="80">
-      <c r="A80" s="1" t="n">
+      <c r="A80" s="2" t="n">
         <v>38899</v>
       </c>
       <c r="B80" t="n">
@@ -2033,7 +2045,7 @@
       </c>
     </row>
     <row r="81">
-      <c r="A81" s="1" t="n">
+      <c r="A81" s="2" t="n">
         <v>38930</v>
       </c>
       <c r="B81" t="n">
@@ -2053,7 +2065,7 @@
       </c>
     </row>
     <row r="82">
-      <c r="A82" s="1" t="n">
+      <c r="A82" s="2" t="n">
         <v>38961</v>
       </c>
       <c r="B82" t="n">
@@ -2073,7 +2085,7 @@
       </c>
     </row>
     <row r="83">
-      <c r="A83" s="1" t="n">
+      <c r="A83" s="2" t="n">
         <v>38991</v>
       </c>
       <c r="B83" t="n">
@@ -2093,7 +2105,7 @@
       </c>
     </row>
     <row r="84">
-      <c r="A84" s="1" t="n">
+      <c r="A84" s="2" t="n">
         <v>39022</v>
       </c>
       <c r="B84" t="n">
@@ -2113,7 +2125,7 @@
       </c>
     </row>
     <row r="85">
-      <c r="A85" s="1" t="n">
+      <c r="A85" s="2" t="n">
         <v>39052</v>
       </c>
       <c r="B85" t="n">
@@ -2133,7 +2145,7 @@
       </c>
     </row>
     <row r="86">
-      <c r="A86" s="1" t="n">
+      <c r="A86" s="2" t="n">
         <v>39083</v>
       </c>
       <c r="B86" t="n">
@@ -2153,7 +2165,7 @@
       </c>
     </row>
     <row r="87">
-      <c r="A87" s="1" t="n">
+      <c r="A87" s="2" t="n">
         <v>39114</v>
       </c>
       <c r="B87" t="n">
@@ -2173,7 +2185,7 @@
       </c>
     </row>
     <row r="88">
-      <c r="A88" s="1" t="n">
+      <c r="A88" s="2" t="n">
         <v>39142</v>
       </c>
       <c r="B88" t="n">
@@ -2193,7 +2205,7 @@
       </c>
     </row>
     <row r="89">
-      <c r="A89" s="1" t="n">
+      <c r="A89" s="2" t="n">
         <v>39173</v>
       </c>
       <c r="B89" t="n">
@@ -2213,7 +2225,7 @@
       </c>
     </row>
     <row r="90">
-      <c r="A90" s="1" t="n">
+      <c r="A90" s="2" t="n">
         <v>39203</v>
       </c>
       <c r="B90" t="n">
@@ -2233,7 +2245,7 @@
       </c>
     </row>
     <row r="91">
-      <c r="A91" s="1" t="n">
+      <c r="A91" s="2" t="n">
         <v>39234</v>
       </c>
       <c r="B91" t="n">
@@ -2253,7 +2265,7 @@
       </c>
     </row>
     <row r="92">
-      <c r="A92" s="1" t="n">
+      <c r="A92" s="2" t="n">
         <v>39264</v>
       </c>
       <c r="B92" t="n">
@@ -2273,7 +2285,7 @@
       </c>
     </row>
     <row r="93">
-      <c r="A93" s="1" t="n">
+      <c r="A93" s="2" t="n">
         <v>39295</v>
       </c>
       <c r="B93" t="n">
@@ -2293,7 +2305,7 @@
       </c>
     </row>
     <row r="94">
-      <c r="A94" s="1" t="n">
+      <c r="A94" s="2" t="n">
         <v>39326</v>
       </c>
       <c r="B94" t="n">
@@ -2313,7 +2325,7 @@
       </c>
     </row>
     <row r="95">
-      <c r="A95" s="1" t="n">
+      <c r="A95" s="2" t="n">
         <v>39356</v>
       </c>
       <c r="B95" t="n">
@@ -2333,7 +2345,7 @@
       </c>
     </row>
     <row r="96">
-      <c r="A96" s="1" t="n">
+      <c r="A96" s="2" t="n">
         <v>39387</v>
       </c>
       <c r="B96" t="n">
@@ -2353,7 +2365,7 @@
       </c>
     </row>
     <row r="97">
-      <c r="A97" s="1" t="n">
+      <c r="A97" s="2" t="n">
         <v>39417</v>
       </c>
       <c r="B97" t="n">
@@ -2373,7 +2385,7 @@
       </c>
     </row>
     <row r="98">
-      <c r="A98" s="1" t="n">
+      <c r="A98" s="2" t="n">
         <v>39448</v>
       </c>
       <c r="B98" t="n">
@@ -2393,7 +2405,7 @@
       </c>
     </row>
     <row r="99">
-      <c r="A99" s="1" t="n">
+      <c r="A99" s="2" t="n">
         <v>39479</v>
       </c>
       <c r="B99" t="n">
@@ -2413,7 +2425,7 @@
       </c>
     </row>
     <row r="100">
-      <c r="A100" s="1" t="n">
+      <c r="A100" s="2" t="n">
         <v>39508</v>
       </c>
       <c r="B100" t="n">
@@ -2433,7 +2445,7 @@
       </c>
     </row>
     <row r="101">
-      <c r="A101" s="1" t="n">
+      <c r="A101" s="2" t="n">
         <v>39539</v>
       </c>
       <c r="B101" t="n">
@@ -2453,7 +2465,7 @@
       </c>
     </row>
     <row r="102">
-      <c r="A102" s="1" t="n">
+      <c r="A102" s="2" t="n">
         <v>39569</v>
       </c>
       <c r="B102" t="n">
@@ -2473,7 +2485,7 @@
       </c>
     </row>
     <row r="103">
-      <c r="A103" s="1" t="n">
+      <c r="A103" s="2" t="n">
         <v>39600</v>
       </c>
       <c r="B103" t="n">
@@ -2493,7 +2505,7 @@
       </c>
     </row>
     <row r="104">
-      <c r="A104" s="1" t="n">
+      <c r="A104" s="2" t="n">
         <v>39630</v>
       </c>
       <c r="B104" t="n">
@@ -2513,7 +2525,7 @@
       </c>
     </row>
     <row r="105">
-      <c r="A105" s="1" t="n">
+      <c r="A105" s="2" t="n">
         <v>39661</v>
       </c>
       <c r="B105" t="n">
@@ -2533,7 +2545,7 @@
       </c>
     </row>
     <row r="106">
-      <c r="A106" s="1" t="n">
+      <c r="A106" s="2" t="n">
         <v>39692</v>
       </c>
       <c r="B106" t="n">
@@ -2553,7 +2565,7 @@
       </c>
     </row>
     <row r="107">
-      <c r="A107" s="1" t="n">
+      <c r="A107" s="2" t="n">
         <v>39722</v>
       </c>
       <c r="B107" t="n">
@@ -2573,7 +2585,7 @@
       </c>
     </row>
     <row r="108">
-      <c r="A108" s="1" t="n">
+      <c r="A108" s="2" t="n">
         <v>39753</v>
       </c>
       <c r="B108" t="n">
@@ -2593,7 +2605,7 @@
       </c>
     </row>
     <row r="109">
-      <c r="A109" s="1" t="n">
+      <c r="A109" s="2" t="n">
         <v>39783</v>
       </c>
       <c r="B109" t="n">
@@ -2613,7 +2625,7 @@
       </c>
     </row>
     <row r="110">
-      <c r="A110" s="1" t="n">
+      <c r="A110" s="2" t="n">
         <v>39814</v>
       </c>
       <c r="B110" t="n">
@@ -2633,7 +2645,7 @@
       </c>
     </row>
     <row r="111">
-      <c r="A111" s="1" t="n">
+      <c r="A111" s="2" t="n">
         <v>39845</v>
       </c>
       <c r="B111" t="n">
@@ -2653,11 +2665,11 @@
       </c>
     </row>
     <row r="112">
-      <c r="A112" s="1" t="n">
+      <c r="A112" s="2" t="n">
         <v>39873</v>
       </c>
       <c r="B112" t="n">
-        <v>13.2460749040845</v>
+        <v>13.24607490408451</v>
       </c>
       <c r="C112" t="n">
         <v>3.07402318029276</v>
@@ -2673,7 +2685,7 @@
       </c>
     </row>
     <row r="113">
-      <c r="A113" s="1" t="n">
+      <c r="A113" s="2" t="n">
         <v>39904</v>
       </c>
       <c r="B113" t="n">
@@ -2693,7 +2705,7 @@
       </c>
     </row>
     <row r="114">
-      <c r="A114" s="1" t="n">
+      <c r="A114" s="2" t="n">
         <v>39934</v>
       </c>
       <c r="B114" t="n">
@@ -2713,11 +2725,11 @@
       </c>
     </row>
     <row r="115">
-      <c r="A115" s="1" t="n">
+      <c r="A115" s="2" t="n">
         <v>39965</v>
       </c>
       <c r="B115" t="n">
-        <v>-15.08860714692284</v>
+        <v>-15.08860714692285</v>
       </c>
       <c r="C115" t="n">
         <v>3.430754526529753</v>
@@ -2733,7 +2745,7 @@
       </c>
     </row>
     <row r="116">
-      <c r="A116" s="1" t="n">
+      <c r="A116" s="2" t="n">
         <v>39995</v>
       </c>
       <c r="B116" t="n">
@@ -2753,7 +2765,7 @@
       </c>
     </row>
     <row r="117">
-      <c r="A117" s="1" t="n">
+      <c r="A117" s="2" t="n">
         <v>40026</v>
       </c>
       <c r="B117" t="n">
@@ -2773,7 +2785,7 @@
       </c>
     </row>
     <row r="118">
-      <c r="A118" s="1" t="n">
+      <c r="A118" s="2" t="n">
         <v>40057</v>
       </c>
       <c r="B118" t="n">
@@ -2793,7 +2805,7 @@
       </c>
     </row>
     <row r="119">
-      <c r="A119" s="1" t="n">
+      <c r="A119" s="2" t="n">
         <v>40087</v>
       </c>
       <c r="B119" t="n">
@@ -2813,7 +2825,7 @@
       </c>
     </row>
     <row r="120">
-      <c r="A120" s="1" t="n">
+      <c r="A120" s="2" t="n">
         <v>40118</v>
       </c>
       <c r="B120" t="n">
@@ -2833,7 +2845,7 @@
       </c>
     </row>
     <row r="121">
-      <c r="A121" s="1" t="n">
+      <c r="A121" s="2" t="n">
         <v>40148</v>
       </c>
       <c r="B121" t="n">
@@ -2853,7 +2865,7 @@
       </c>
     </row>
     <row r="122">
-      <c r="A122" s="1" t="n">
+      <c r="A122" s="2" t="n">
         <v>40179</v>
       </c>
       <c r="B122" t="n">
@@ -2873,7 +2885,7 @@
       </c>
     </row>
     <row r="123">
-      <c r="A123" s="1" t="n">
+      <c r="A123" s="2" t="n">
         <v>40210</v>
       </c>
       <c r="B123" t="n">
@@ -2893,7 +2905,7 @@
       </c>
     </row>
     <row r="124">
-      <c r="A124" s="1" t="n">
+      <c r="A124" s="2" t="n">
         <v>40238</v>
       </c>
       <c r="B124" t="n">
@@ -2913,7 +2925,7 @@
       </c>
     </row>
     <row r="125">
-      <c r="A125" s="1" t="n">
+      <c r="A125" s="2" t="n">
         <v>40269</v>
       </c>
       <c r="B125" t="n">
@@ -2933,7 +2945,7 @@
       </c>
     </row>
     <row r="126">
-      <c r="A126" s="1" t="n">
+      <c r="A126" s="2" t="n">
         <v>40299</v>
       </c>
       <c r="B126" t="n">
@@ -2953,7 +2965,7 @@
       </c>
     </row>
     <row r="127">
-      <c r="A127" s="1" t="n">
+      <c r="A127" s="2" t="n">
         <v>40330</v>
       </c>
       <c r="B127" t="n">
@@ -2973,7 +2985,7 @@
       </c>
     </row>
     <row r="128">
-      <c r="A128" s="1" t="n">
+      <c r="A128" s="2" t="n">
         <v>40360</v>
       </c>
       <c r="B128" t="n">
@@ -2993,7 +3005,7 @@
       </c>
     </row>
     <row r="129">
-      <c r="A129" s="1" t="n">
+      <c r="A129" s="2" t="n">
         <v>40391</v>
       </c>
       <c r="B129" t="n">
@@ -3013,7 +3025,7 @@
       </c>
     </row>
     <row r="130">
-      <c r="A130" s="1" t="n">
+      <c r="A130" s="2" t="n">
         <v>40422</v>
       </c>
       <c r="B130" t="n">
@@ -3033,7 +3045,7 @@
       </c>
     </row>
     <row r="131">
-      <c r="A131" s="1" t="n">
+      <c r="A131" s="2" t="n">
         <v>40452</v>
       </c>
       <c r="B131" t="n">
@@ -3053,7 +3065,7 @@
       </c>
     </row>
     <row r="132">
-      <c r="A132" s="1" t="n">
+      <c r="A132" s="2" t="n">
         <v>40483</v>
       </c>
       <c r="B132" t="n">
@@ -3073,7 +3085,7 @@
       </c>
     </row>
     <row r="133">
-      <c r="A133" s="1" t="n">
+      <c r="A133" s="2" t="n">
         <v>40513</v>
       </c>
       <c r="B133" t="n">
@@ -3093,7 +3105,7 @@
       </c>
     </row>
     <row r="134">
-      <c r="A134" s="1" t="n">
+      <c r="A134" s="2" t="n">
         <v>40544</v>
       </c>
       <c r="B134" t="n">
@@ -3113,7 +3125,7 @@
       </c>
     </row>
     <row r="135">
-      <c r="A135" s="1" t="n">
+      <c r="A135" s="2" t="n">
         <v>40575</v>
       </c>
       <c r="B135" t="n">
@@ -3133,7 +3145,7 @@
       </c>
     </row>
     <row r="136">
-      <c r="A136" s="1" t="n">
+      <c r="A136" s="2" t="n">
         <v>40603</v>
       </c>
       <c r="B136" t="n">
@@ -3153,7 +3165,7 @@
       </c>
     </row>
     <row r="137">
-      <c r="A137" s="1" t="n">
+      <c r="A137" s="2" t="n">
         <v>40634</v>
       </c>
       <c r="B137" t="n">
@@ -3173,7 +3185,7 @@
       </c>
     </row>
     <row r="138">
-      <c r="A138" s="1" t="n">
+      <c r="A138" s="2" t="n">
         <v>40664</v>
       </c>
       <c r="B138" t="n">
@@ -3193,7 +3205,7 @@
       </c>
     </row>
     <row r="139">
-      <c r="A139" s="1" t="n">
+      <c r="A139" s="2" t="n">
         <v>40695</v>
       </c>
       <c r="B139" t="n">
@@ -3213,7 +3225,7 @@
       </c>
     </row>
     <row r="140">
-      <c r="A140" s="1" t="n">
+      <c r="A140" s="2" t="n">
         <v>40725</v>
       </c>
       <c r="B140" t="n">
@@ -3233,7 +3245,7 @@
       </c>
     </row>
     <row r="141">
-      <c r="A141" s="1" t="n">
+      <c r="A141" s="2" t="n">
         <v>40756</v>
       </c>
       <c r="B141" t="n">
@@ -3253,7 +3265,7 @@
       </c>
     </row>
     <row r="142">
-      <c r="A142" s="1" t="n">
+      <c r="A142" s="2" t="n">
         <v>40787</v>
       </c>
       <c r="B142" t="n">
@@ -3273,11 +3285,11 @@
       </c>
     </row>
     <row r="143">
-      <c r="A143" s="1" t="n">
+      <c r="A143" s="2" t="n">
         <v>40817</v>
       </c>
       <c r="B143" t="n">
-        <v>9.26176652574722</v>
+        <v>9.261766525747221</v>
       </c>
       <c r="C143" t="n">
         <v>3.806196866255272</v>
@@ -3293,7 +3305,7 @@
       </c>
     </row>
     <row r="144">
-      <c r="A144" s="1" t="n">
+      <c r="A144" s="2" t="n">
         <v>40848</v>
       </c>
       <c r="B144" t="n">
@@ -3313,7 +3325,7 @@
       </c>
     </row>
     <row r="145">
-      <c r="A145" s="1" t="n">
+      <c r="A145" s="2" t="n">
         <v>40878</v>
       </c>
       <c r="B145" t="n">
@@ -3333,7 +3345,7 @@
       </c>
     </row>
     <row r="146">
-      <c r="A146" s="1" t="n">
+      <c r="A146" s="2" t="n">
         <v>40909</v>
       </c>
       <c r="B146" t="n">
@@ -3353,7 +3365,7 @@
       </c>
     </row>
     <row r="147">
-      <c r="A147" s="1" t="n">
+      <c r="A147" s="2" t="n">
         <v>40940</v>
       </c>
       <c r="B147" t="n">
@@ -3373,7 +3385,7 @@
       </c>
     </row>
     <row r="148">
-      <c r="A148" s="1" t="n">
+      <c r="A148" s="2" t="n">
         <v>40969</v>
       </c>
       <c r="B148" t="n">
@@ -3393,11 +3405,11 @@
       </c>
     </row>
     <row r="149">
-      <c r="A149" s="1" t="n">
+      <c r="A149" s="2" t="n">
         <v>41000</v>
       </c>
       <c r="B149" t="n">
-        <v>-3.768373197178725</v>
+        <v>-3.768373197178724</v>
       </c>
       <c r="C149" t="n">
         <v>3.857750690414038</v>
@@ -3413,7 +3425,7 @@
       </c>
     </row>
     <row r="150">
-      <c r="A150" s="1" t="n">
+      <c r="A150" s="2" t="n">
         <v>41030</v>
       </c>
       <c r="B150" t="n">
@@ -3433,7 +3445,7 @@
       </c>
     </row>
     <row r="151">
-      <c r="A151" s="1" t="n">
+      <c r="A151" s="2" t="n">
         <v>41061</v>
       </c>
       <c r="B151" t="n">
@@ -3453,7 +3465,7 @@
       </c>
     </row>
     <row r="152">
-      <c r="A152" s="1" t="n">
+      <c r="A152" s="2" t="n">
         <v>41091</v>
       </c>
       <c r="B152" t="n">
@@ -3473,11 +3485,11 @@
       </c>
     </row>
     <row r="153">
-      <c r="A153" s="1" t="n">
+      <c r="A153" s="2" t="n">
         <v>41122</v>
       </c>
       <c r="B153" t="n">
-        <v>-0.1021760088819951</v>
+        <v>-0.1021760088819952</v>
       </c>
       <c r="C153" t="n">
         <v>3.742570727008806</v>
@@ -3493,7 +3505,7 @@
       </c>
     </row>
     <row r="154">
-      <c r="A154" s="1" t="n">
+      <c r="A154" s="2" t="n">
         <v>41153</v>
       </c>
       <c r="B154" t="n">
@@ -3513,7 +3525,7 @@
       </c>
     </row>
     <row r="155">
-      <c r="A155" s="1" t="n">
+      <c r="A155" s="2" t="n">
         <v>41183</v>
       </c>
       <c r="B155" t="n">
@@ -3533,7 +3545,7 @@
       </c>
     </row>
     <row r="156">
-      <c r="A156" s="1" t="n">
+      <c r="A156" s="2" t="n">
         <v>41214</v>
       </c>
       <c r="B156" t="n">
@@ -3553,7 +3565,7 @@
       </c>
     </row>
     <row r="157">
-      <c r="A157" s="1" t="n">
+      <c r="A157" s="2" t="n">
         <v>41244</v>
       </c>
       <c r="B157" t="n">
@@ -3573,7 +3585,7 @@
       </c>
     </row>
     <row r="158">
-      <c r="A158" s="1" t="n">
+      <c r="A158" s="2" t="n">
         <v>41275</v>
       </c>
       <c r="B158" t="n">
@@ -3593,7 +3605,7 @@
       </c>
     </row>
     <row r="159">
-      <c r="A159" s="1" t="n">
+      <c r="A159" s="2" t="n">
         <v>41306</v>
       </c>
       <c r="B159" t="n">
@@ -3613,7 +3625,7 @@
       </c>
     </row>
     <row r="160">
-      <c r="A160" s="1" t="n">
+      <c r="A160" s="2" t="n">
         <v>41334</v>
       </c>
       <c r="B160" t="n">
@@ -3633,7 +3645,7 @@
       </c>
     </row>
     <row r="161">
-      <c r="A161" s="1" t="n">
+      <c r="A161" s="2" t="n">
         <v>41365</v>
       </c>
       <c r="B161" t="n">
@@ -3653,7 +3665,7 @@
       </c>
     </row>
     <row r="162">
-      <c r="A162" s="1" t="n">
+      <c r="A162" s="2" t="n">
         <v>41395</v>
       </c>
       <c r="B162" t="n">
@@ -3673,11 +3685,11 @@
       </c>
     </row>
     <row r="163">
-      <c r="A163" s="1" t="n">
+      <c r="A163" s="2" t="n">
         <v>41426</v>
       </c>
       <c r="B163" t="n">
-        <v>-2.126261964223034</v>
+        <v>-2.126261964223033</v>
       </c>
       <c r="C163" t="n">
         <v>3.73297856993634</v>
@@ -3693,7 +3705,7 @@
       </c>
     </row>
     <row r="164">
-      <c r="A164" s="1" t="n">
+      <c r="A164" s="2" t="n">
         <v>41456</v>
       </c>
       <c r="B164" t="n">
@@ -3713,7 +3725,7 @@
       </c>
     </row>
     <row r="165">
-      <c r="A165" s="1" t="n">
+      <c r="A165" s="2" t="n">
         <v>41487</v>
       </c>
       <c r="B165" t="n">
@@ -3733,7 +3745,7 @@
       </c>
     </row>
     <row r="166">
-      <c r="A166" s="1" t="n">
+      <c r="A166" s="2" t="n">
         <v>41518</v>
       </c>
       <c r="B166" t="n">
@@ -3753,7 +3765,7 @@
       </c>
     </row>
     <row r="167">
-      <c r="A167" s="1" t="n">
+      <c r="A167" s="2" t="n">
         <v>41548</v>
       </c>
       <c r="B167" t="n">
@@ -3773,7 +3785,7 @@
       </c>
     </row>
     <row r="168">
-      <c r="A168" s="1" t="n">
+      <c r="A168" s="2" t="n">
         <v>41579</v>
       </c>
       <c r="B168" t="n">
@@ -3793,7 +3805,7 @@
       </c>
     </row>
     <row r="169">
-      <c r="A169" s="1" t="n">
+      <c r="A169" s="2" t="n">
         <v>41609</v>
       </c>
       <c r="B169" t="n">
@@ -3813,7 +3825,7 @@
       </c>
     </row>
     <row r="170">
-      <c r="A170" s="1" t="n">
+      <c r="A170" s="2" t="n">
         <v>41640</v>
       </c>
       <c r="B170" t="n">
@@ -3833,7 +3845,7 @@
       </c>
     </row>
     <row r="171">
-      <c r="A171" s="1" t="n">
+      <c r="A171" s="2" t="n">
         <v>41671</v>
       </c>
       <c r="B171" t="n">
@@ -3853,7 +3865,7 @@
       </c>
     </row>
     <row r="172">
-      <c r="A172" s="1" t="n">
+      <c r="A172" s="2" t="n">
         <v>41699</v>
       </c>
       <c r="B172" t="n">
@@ -3873,7 +3885,7 @@
       </c>
     </row>
     <row r="173">
-      <c r="A173" s="1" t="n">
+      <c r="A173" s="2" t="n">
         <v>41730</v>
       </c>
       <c r="B173" t="n">
@@ -3893,7 +3905,7 @@
       </c>
     </row>
     <row r="174">
-      <c r="A174" s="1" t="n">
+      <c r="A174" s="2" t="n">
         <v>41760</v>
       </c>
       <c r="B174" t="n">
@@ -3913,7 +3925,7 @@
       </c>
     </row>
     <row r="175">
-      <c r="A175" s="1" t="n">
+      <c r="A175" s="2" t="n">
         <v>41791</v>
       </c>
       <c r="B175" t="n">
@@ -3933,7 +3945,7 @@
       </c>
     </row>
     <row r="176">
-      <c r="A176" s="1" t="n">
+      <c r="A176" s="2" t="n">
         <v>41821</v>
       </c>
       <c r="B176" t="n">
@@ -3953,7 +3965,7 @@
       </c>
     </row>
     <row r="177">
-      <c r="A177" s="1" t="n">
+      <c r="A177" s="2" t="n">
         <v>41852</v>
       </c>
       <c r="B177" t="n">
@@ -3973,7 +3985,7 @@
       </c>
     </row>
     <row r="178">
-      <c r="A178" s="1" t="n">
+      <c r="A178" s="2" t="n">
         <v>41883</v>
       </c>
       <c r="B178" t="n">
@@ -3993,7 +4005,7 @@
       </c>
     </row>
     <row r="179">
-      <c r="A179" s="1" t="n">
+      <c r="A179" s="2" t="n">
         <v>41913</v>
       </c>
       <c r="B179" t="n">
@@ -4013,7 +4025,7 @@
       </c>
     </row>
     <row r="180">
-      <c r="A180" s="1" t="n">
+      <c r="A180" s="2" t="n">
         <v>41944</v>
       </c>
       <c r="B180" t="n">
@@ -4033,7 +4045,7 @@
       </c>
     </row>
     <row r="181">
-      <c r="A181" s="1" t="n">
+      <c r="A181" s="2" t="n">
         <v>41974</v>
       </c>
       <c r="B181" t="n">
